--- a/Project Outputs for UZ_A_DAC/Rev02/BOM/BOM_JLC-UZ_A_DAC(THS).xlsx
+++ b/Project Outputs for UZ_A_DAC/Rev02/BOM/BOM_JLC-UZ_A_DAC(THS).xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\UltraZohm\pcb_design\uz_a_dac8831\Project Outputs for UZ_A_DAC\Rev01\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\UltraZohm\pcb_design\uz_a_dac8831\Project Outputs for UZ_A_DAC\Rev02\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{626F702A-078A-4417-A239-22E26FD2649D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E6BDD709-1DE7-46C5-9FB4-7299688ABDA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="47895" yWindow="-2220" windowWidth="19410" windowHeight="20985" xr2:uid="{8EB92CD4-8990-4A58-AC57-FDF9BBF21F69}"/>
+    <workbookView xWindow="29940" yWindow="1140" windowWidth="21600" windowHeight="11175" xr2:uid="{8113F31D-CB11-498B-A703-8088901740EE}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM_JLC-UZ_A_DAC(THS)" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="284">
   <si>
     <t>Quantity</t>
   </si>
@@ -401,6 +401,15 @@
     <t>SMT_inductor_1050</t>
   </si>
   <si>
+    <t>Mounting Hole</t>
+  </si>
+  <si>
+    <t>MH9, MH10</t>
+  </si>
+  <si>
+    <t>MH_3.4</t>
+  </si>
+  <si>
     <t>IPL1-102-01-L-S-K</t>
   </si>
   <si>
@@ -575,6 +584,9 @@
     <t>RK73B1JTTD103J</t>
   </si>
   <si>
+    <t>[NoParam], C25804</t>
+  </si>
+  <si>
     <t>9k1</t>
   </si>
   <si>
@@ -671,6 +683,36 @@
     <t>C25803</t>
   </si>
   <si>
+    <t>Serial #</t>
+  </si>
+  <si>
+    <t>Serial1</t>
+  </si>
+  <si>
+    <t>PCB Manufacturer</t>
+  </si>
+  <si>
+    <t>Field to put in a serial number</t>
+  </si>
+  <si>
+    <t>SERIAL</t>
+  </si>
+  <si>
+    <t>Serial Number</t>
+  </si>
+  <si>
+    <t>TP4, TP5, TP8, TP9, TP10, TP11, TP12, TP13, TP14, TP15A, TP15B, TP15C, TP15D, TP15E, TP15F, TP15G, TP15H, TP16A, TP16B, TP16C, TP16D, TP16E, TP16F, TP16G, TP16H, TP17A, TP17B, TP17C, TP17D, TP17E, TP17F, TP17G, TP17H, TP18</t>
+  </si>
+  <si>
+    <t>TP</t>
+  </si>
+  <si>
+    <t>Test Point 1 mm</t>
+  </si>
+  <si>
+    <t>TP_1mm</t>
+  </si>
+  <si>
     <t>M24C02-WMN6TP</t>
   </si>
   <si>
@@ -833,6 +875,15 @@
     <t>SOP50P640X120-38N</t>
   </si>
   <si>
+    <t>HSEC8-140-01-XX-DV-A-BL-CARD</t>
+  </si>
+  <si>
+    <t>X2</t>
+  </si>
+  <si>
+    <t>Mating Card Layout for HSEC8-140-01-XX-DV-A-BL-CARD</t>
+  </si>
+  <si>
     <t>IPL1-108-01-L-D-RA-K</t>
   </si>
   <si>
@@ -840,159 +891,6 @@
   </si>
   <si>
     <t>2.54 mm Double Row Termin Assembly (right angle)</t>
-  </si>
-  <si>
-    <t>C2679800</t>
-  </si>
-  <si>
-    <t>C17522910</t>
-  </si>
-  <si>
-    <t>C2058004</t>
-  </si>
-  <si>
-    <t>C702015</t>
-  </si>
-  <si>
-    <t>C16092</t>
-  </si>
-  <si>
-    <t>C673300</t>
-  </si>
-  <si>
-    <t>C2058426</t>
-  </si>
-  <si>
-    <t>C23920</t>
-  </si>
-  <si>
-    <t>C2867754</t>
-  </si>
-  <si>
-    <t>C632040</t>
-  </si>
-  <si>
-    <t>C893329</t>
-  </si>
-  <si>
-    <t>C1355331</t>
-  </si>
-  <si>
-    <t>C3016454</t>
-  </si>
-  <si>
-    <t>C351630</t>
-  </si>
-  <si>
-    <t>C844584</t>
-  </si>
-  <si>
-    <t>C2074771</t>
-  </si>
-  <si>
-    <t>C269717</t>
-  </si>
-  <si>
-    <t>C269704</t>
-  </si>
-  <si>
-    <t>C25804</t>
-  </si>
-  <si>
-    <t>C2089686</t>
-  </si>
-  <si>
-    <t>C861659</t>
-  </si>
-  <si>
-    <t>C861688</t>
-  </si>
-  <si>
-    <t>C861734</t>
-  </si>
-  <si>
-    <t>C269481</t>
-  </si>
-  <si>
-    <t>C325635</t>
-  </si>
-  <si>
-    <t>C2075108</t>
-  </si>
-  <si>
-    <t>C2692855</t>
-  </si>
-  <si>
-    <t>C2692779</t>
-  </si>
-  <si>
-    <t>C849824</t>
-  </si>
-  <si>
-    <t>C5728185</t>
-  </si>
-  <si>
-    <t>C2045822</t>
-  </si>
-  <si>
-    <t>C2661857</t>
-  </si>
-  <si>
-    <t>C2454980</t>
-  </si>
-  <si>
-    <t>C464647</t>
-  </si>
-  <si>
-    <t>C89809</t>
-  </si>
-  <si>
-    <t>C84266</t>
-  </si>
-  <si>
-    <t>C84263</t>
-  </si>
-  <si>
-    <t>C4747957</t>
-  </si>
-  <si>
-    <t>C338104</t>
-  </si>
-  <si>
-    <t>C5354993</t>
-  </si>
-  <si>
-    <t>C2857999</t>
-  </si>
-  <si>
-    <t>C918827</t>
-  </si>
-  <si>
-    <t>C499510</t>
-  </si>
-  <si>
-    <t>C1856507</t>
-  </si>
-  <si>
-    <t>C149618</t>
-  </si>
-  <si>
-    <t>C519510</t>
-  </si>
-  <si>
-    <t>C513774</t>
-  </si>
-  <si>
-    <t>C726594</t>
-  </si>
-  <si>
-    <t>C107185</t>
-  </si>
-  <si>
-    <t>C2992614</t>
-  </si>
-  <si>
-    <t>C1853344</t>
   </si>
 </sst>
 </file>
@@ -1049,15 +947,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1371,8 +1266,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA835F02-90E0-46D5-96C3-B9AA0DEAF99F}">
-  <dimension ref="A1:K60"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BAEF866-C63A-4F98-A0DC-2B1CAA6E723F}">
+  <dimension ref="A1:K64"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.26953125" customWidth="1"/>
@@ -1384,8 +1279,7 @@
     <col min="7" max="7" width="23.54296875" customWidth="1"/>
     <col min="8" max="8" width="8.453125" customWidth="1"/>
     <col min="9" max="9" width="9.7265625" customWidth="1"/>
-    <col min="10" max="10" width="27.90625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16" customWidth="1"/>
+    <col min="10" max="11" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.35">
@@ -1450,9 +1344,7 @@
       <c r="J2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="K2" s="5" t="s">
-        <v>310</v>
-      </c>
+      <c r="K2" s="1"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
@@ -1512,9 +1404,7 @@
       <c r="J4" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K4" s="1" t="s">
-        <v>314</v>
-      </c>
+      <c r="K4" s="1"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
@@ -1543,9 +1433,7 @@
       <c r="J5" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="K5" s="1" t="s">
-        <v>315</v>
-      </c>
+      <c r="K5" s="1"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
@@ -1574,9 +1462,7 @@
       <c r="J6" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="K6" s="1" t="s">
-        <v>316</v>
-      </c>
+      <c r="K6" s="1"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
@@ -1605,9 +1491,7 @@
       <c r="J7" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="K7" s="1" t="s">
-        <v>317</v>
-      </c>
+      <c r="K7" s="1"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
@@ -1636,9 +1520,7 @@
       <c r="J8" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="K8" s="1" t="s">
-        <v>311</v>
-      </c>
+      <c r="K8" s="1"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
@@ -1667,9 +1549,7 @@
       <c r="J9" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="K9" s="1" t="s">
-        <v>312</v>
-      </c>
+      <c r="K9" s="1"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
@@ -1698,9 +1578,7 @@
       <c r="J10" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="K10" s="1" t="s">
-        <v>313</v>
-      </c>
+      <c r="K10" s="1"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
@@ -1729,9 +1607,7 @@
       <c r="J11" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="K11" s="1" t="s">
-        <v>304</v>
-      </c>
+      <c r="K11" s="1"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
@@ -1760,9 +1636,7 @@
       <c r="J12" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="K12" s="1" t="s">
-        <v>305</v>
-      </c>
+      <c r="K12" s="1"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
@@ -1791,9 +1665,7 @@
       <c r="J13" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="K13" s="1" t="s">
-        <v>306</v>
-      </c>
+      <c r="K13" s="1"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
@@ -1822,9 +1694,7 @@
       <c r="J14" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="K14" s="1" t="s">
-        <v>307</v>
-      </c>
+      <c r="K14" s="1"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
@@ -1853,9 +1723,7 @@
       <c r="J15" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="K15" s="1" t="s">
-        <v>308</v>
-      </c>
+      <c r="K15" s="1"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
@@ -1884,9 +1752,7 @@
       <c r="J16" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="K16" s="1" t="s">
-        <v>309</v>
-      </c>
+      <c r="K16" s="1"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
@@ -1913,9 +1779,7 @@
       <c r="J17" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="K17" s="1" t="s">
-        <v>301</v>
-      </c>
+      <c r="K17" s="1"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
@@ -1942,9 +1806,7 @@
       <c r="J18" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="K18" s="1" t="s">
-        <v>302</v>
-      </c>
+      <c r="K18" s="1"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
@@ -1971,9 +1833,7 @@
       <c r="J19" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="K19" s="1" t="s">
-        <v>303</v>
-      </c>
+      <c r="K19" s="1"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
@@ -2000,9 +1860,7 @@
       <c r="J20" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="K20" s="1" t="s">
-        <v>300</v>
-      </c>
+      <c r="K20" s="1"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
@@ -2031,9 +1889,7 @@
       <c r="J21" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="K21" s="1" t="s">
-        <v>299</v>
-      </c>
+      <c r="K21" s="1"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
@@ -2062,9 +1918,7 @@
       <c r="J22" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="K22" s="1" t="s">
-        <v>298</v>
-      </c>
+      <c r="K22" s="1"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
@@ -2093,13 +1947,11 @@
       <c r="J23" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="K23" s="1" t="s">
-        <v>297</v>
-      </c>
+      <c r="K23" s="1"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>120</v>
@@ -2108,147 +1960,139 @@
         <v>121</v>
       </c>
       <c r="D24" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="G24" s="2" t="s">
         <v>122</v>
-      </c>
-      <c r="E24" s="1"/>
-      <c r="F24" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>124</v>
       </c>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
       <c r="J24" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="K24" s="1" t="s">
-        <v>296</v>
-      </c>
+      <c r="K24" s="1"/>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B25" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="E25" s="1"/>
+      <c r="F25" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="G25" s="2" t="s">
         <v>127</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>129</v>
       </c>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
       <c r="J25" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="K25" s="2" t="s">
-        <v>131</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="K25" s="1"/>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="G26" s="2" t="s">
         <v>132</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>129</v>
       </c>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
       <c r="J26" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="K26" s="1" t="s">
-        <v>290</v>
+        <v>133</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="D27" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F27" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>128</v>
-      </c>
       <c r="G27" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
       <c r="J27" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="K27" s="1" t="s">
-        <v>291</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="K27" s="1"/>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B28" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="D28" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>138</v>
-      </c>
       <c r="E28" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
       <c r="J28" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="K28" s="1" t="s">
-        <v>292</v>
-      </c>
+      <c r="K28" s="1"/>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
@@ -2261,25 +2105,23 @@
         <v>144</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>143</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
       <c r="J29" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="K29" s="1" t="s">
-        <v>293</v>
-      </c>
+      <c r="K29" s="1"/>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
@@ -2292,117 +2134,111 @@
         <v>147</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>146</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
       <c r="J30" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="K30" s="1" t="s">
-        <v>294</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="K30" s="1"/>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>1</v>
       </c>
       <c r="B31" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="D31" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="D31" s="2" t="s">
-        <v>152</v>
-      </c>
       <c r="E31" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
       <c r="J31" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="K31" s="1" t="s">
-        <v>295</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="K31" s="1"/>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="B32" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="D32" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="D32" s="2" t="s">
-        <v>152</v>
-      </c>
       <c r="E32" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
       <c r="J32" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="K32" s="2" t="s">
-        <v>157</v>
-      </c>
+      <c r="K32" s="1"/>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="B33" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C33" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="C33" s="2" t="s">
-        <v>159</v>
-      </c>
       <c r="D33" s="2" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
       <c r="J33" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="K33" s="1" t="s">
-        <v>288</v>
+        <v>159</v>
+      </c>
+      <c r="K33" s="2" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.35">
@@ -2410,31 +2246,29 @@
         <v>1</v>
       </c>
       <c r="B34" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="D34" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="D34" s="2" t="s">
-        <v>148</v>
-      </c>
       <c r="E34" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
       <c r="J34" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="K34" s="1" t="s">
-        <v>289</v>
-      </c>
+      <c r="K34" s="1"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A35" s="1">
@@ -2447,25 +2281,23 @@
         <v>166</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>165</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
       <c r="J35" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="K35" s="1" t="s">
-        <v>287</v>
-      </c>
+      <c r="K35" s="1"/>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A36" s="1">
@@ -2478,25 +2310,23 @@
         <v>169</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>168</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
       <c r="J36" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="K36" s="1" t="s">
-        <v>286</v>
-      </c>
+      <c r="K36" s="1"/>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
@@ -2509,60 +2339,58 @@
         <v>172</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>138</v>
+        <v>163</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>171</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
       <c r="J37" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="K37" s="2" t="s">
-        <v>174</v>
-      </c>
+      <c r="K37" s="1"/>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A38" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B38" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="C38" s="2" t="s">
-        <v>176</v>
-      </c>
       <c r="D38" s="2" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
       <c r="J38" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="K38" s="2" t="s">
         <v>177</v>
-      </c>
-      <c r="K38" s="2" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A39" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>178</v>
@@ -2571,16 +2399,16 @@
         <v>179</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>178</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
@@ -2593,7 +2421,7 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A40" s="1">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>182</v>
@@ -2602,24 +2430,24 @@
         <v>183</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>182</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
       <c r="J40" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="K40" s="1" t="s">
-        <v>283</v>
+      <c r="K40" s="2" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.35">
@@ -2627,66 +2455,62 @@
         <v>16</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C41" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E41" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="D41" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>185</v>
-      </c>
       <c r="F41" s="2" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
       <c r="J41" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="K41" s="1" t="s">
-        <v>284</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="K41" s="1"/>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C42" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E42" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="D42" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>188</v>
-      </c>
       <c r="F42" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
       <c r="J42" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="K42" s="1" t="s">
-        <v>282</v>
-      </c>
+      <c r="K42" s="1"/>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A43" s="1">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>192</v>
@@ -2695,60 +2519,56 @@
         <v>193</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>138</v>
+        <v>194</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>192</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
       <c r="J43" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="K43" s="1" t="s">
-        <v>281</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="K43" s="1"/>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A44" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C44" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E44" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="D44" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>195</v>
-      </c>
       <c r="F44" s="2" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
       <c r="J44" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="K44" s="2" t="s">
         <v>198</v>
       </c>
+      <c r="K44" s="1"/>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A45" s="1">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>199</v>
@@ -2757,60 +2577,58 @@
         <v>200</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>199</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
       <c r="J45" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="K45" s="1" t="s">
-        <v>280</v>
+      <c r="K45" s="2" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A46" s="1">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C46" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E46" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="D46" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>202</v>
-      </c>
       <c r="F46" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
       <c r="J46" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="K46" s="1" t="s">
-        <v>279</v>
-      </c>
+      <c r="K46" s="1"/>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A47" s="1">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>206</v>
@@ -2819,29 +2637,27 @@
         <v>207</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>138</v>
+        <v>208</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>206</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="H47" s="1"/>
       <c r="I47" s="1"/>
       <c r="J47" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="K47" s="2" t="s">
         <v>209</v>
       </c>
+      <c r="K47" s="1"/>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A48" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>210</v>
@@ -2850,24 +2666,24 @@
         <v>211</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>212</v>
+        <v>141</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>210</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>213</v>
+        <v>131</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>214</v>
+        <v>132</v>
       </c>
       <c r="H48" s="1"/>
       <c r="I48" s="1"/>
       <c r="J48" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.35">
@@ -2875,86 +2691,86 @@
         <v>1</v>
       </c>
       <c r="B49" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D49" s="2" t="s">
         <v>216</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>218</v>
       </c>
       <c r="E49" s="1"/>
       <c r="F49" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
       <c r="J49" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="K49" s="1" t="s">
-        <v>278</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="K49" s="1"/>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A50" s="1">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="B50" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E50" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="F50" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="D50" s="2" t="s">
+      <c r="G50" s="2" t="s">
         <v>223</v>
-      </c>
-      <c r="E50" s="1"/>
-      <c r="F50" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="G50" s="2" t="s">
-        <v>225</v>
       </c>
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
       <c r="J50" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="K50" s="1" t="s">
-        <v>277</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="K50" s="1"/>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A51" s="1">
         <v>1</v>
       </c>
       <c r="B51" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="D51" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="E51" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="F51" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="D51" s="2" t="s">
+      <c r="G51" s="2" t="s">
         <v>228</v>
-      </c>
-      <c r="E51" s="1"/>
-      <c r="F51" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="G51" s="2" t="s">
-        <v>230</v>
       </c>
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
       <c r="J51" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="K51" s="1" t="s">
-        <v>276</v>
+        <v>224</v>
+      </c>
+      <c r="K51" s="2" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.35">
@@ -2962,13 +2778,13 @@
         <v>1</v>
       </c>
       <c r="B52" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C52" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="D52" s="2" t="s">
         <v>232</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>218</v>
       </c>
       <c r="E52" s="1"/>
       <c r="F52" s="2" t="s">
@@ -2980,11 +2796,9 @@
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
       <c r="J52" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="K52" s="1" t="s">
-        <v>274</v>
-      </c>
+        <v>230</v>
+      </c>
+      <c r="K52" s="1"/>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A53" s="1">
@@ -2997,226 +2811,320 @@
         <v>236</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>218</v>
+        <v>237</v>
       </c>
       <c r="E53" s="1"/>
       <c r="F53" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
       <c r="J53" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="K53" s="1" t="s">
-        <v>275</v>
-      </c>
+      <c r="K53" s="1"/>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A54" s="1">
         <v>1</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>218</v>
+        <v>242</v>
       </c>
       <c r="E54" s="1"/>
       <c r="F54" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
       <c r="J54" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="K54" s="1" t="s">
-        <v>273</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="K54" s="1"/>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A55" s="1">
         <v>1</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>245</v>
+        <v>232</v>
       </c>
       <c r="E55" s="1"/>
       <c r="F55" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H55" s="1"/>
       <c r="I55" s="1"/>
       <c r="J55" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="K55" s="1" t="s">
-        <v>272</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="K55" s="1"/>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A56" s="1">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="E56" s="1"/>
       <c r="F56" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
       <c r="J56" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="K56" s="1" t="s">
-        <v>271</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="K56" s="1"/>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A57" s="1">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="E57" s="1"/>
       <c r="F57" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H57" s="1"/>
       <c r="I57" s="1"/>
       <c r="J57" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="K57" s="1" t="s">
-        <v>269</v>
-      </c>
+        <v>253</v>
+      </c>
+      <c r="K57" s="1"/>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A58" s="1">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>218</v>
+        <v>259</v>
       </c>
       <c r="E58" s="1"/>
       <c r="F58" s="2" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="H58" s="1"/>
       <c r="I58" s="1"/>
       <c r="J58" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="K58" s="1" t="s">
-        <v>267</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="K58" s="1"/>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A59" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="E59" s="1"/>
       <c r="F59" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="H59" s="1"/>
       <c r="I59" s="1"/>
       <c r="J59" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="K59" s="1" t="s">
-        <v>270</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="K59" s="1"/>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A60" s="1">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>122</v>
+        <v>232</v>
       </c>
       <c r="E60" s="1"/>
       <c r="F60" s="2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
       <c r="J60" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="K60" s="1" t="s">
-        <v>268</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="K60" s="1"/>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A61" s="1">
+        <v>8</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="E61" s="1"/>
+      <c r="F61" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="H61" s="1"/>
+      <c r="I61" s="1"/>
+      <c r="J61" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="K61" s="1"/>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A62" s="1">
+        <v>2</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="E62" s="1"/>
+      <c r="F62" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="K62" s="1"/>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A63" s="1">
+        <v>1</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="H63" s="1"/>
+      <c r="I63" s="1"/>
+      <c r="J63" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="K63" s="1"/>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A64" s="1">
+        <v>1</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="E64" s="1"/>
+      <c r="F64" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="H64" s="1"/>
+      <c r="I64" s="1"/>
+      <c r="J64" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="K64" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
